--- a/rtos-api-analysis/results/rt-thread_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/rt-thread_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174956.8292682927</v>
+        <v>119042.8195121951</v>
       </c>
       <c r="C2" t="n">
-        <v>1023.139352446156</v>
+        <v>704.3953817289653</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>3704.759250480937</v>
+        <v>2622.44033748831</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>24396</v>
+        <v>17514</v>
       </c>
       <c r="H2" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I2" t="n">
         <v>206</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
